--- a/Danh_Sach_Group_Telegram_SCM.xlsx
+++ b/Danh_Sach_Group_Telegram_SCM.xlsx
@@ -4466,12 +4466,12 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20/10/2026 09:05</t>
+          <t>20/10/2026 06:12</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>[KRC] [Hình ảnh / Chứng từ]</t>
+          <t>[KRC] Xoài tứ quý thiếu 200g</t>
         </is>
       </c>
       <c r="K73" t="n">
@@ -29147,12 +29147,12 @@
       </c>
       <c r="K282" t="inlineStr">
         <is>
-          <t>[Hình ảnh / Chứng từ]</t>
+          <t>Xoài tứ quý thiếu 200g</t>
         </is>
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>20/10/2026 09:05</t>
+          <t>20/10/2026 06:12</t>
         </is>
       </c>
       <c r="M282" t="n">
